--- a/translation dict_V2.xlsx
+++ b/translation dict_V2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E416"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8909,1456 +8909,25 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Nationality</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Administrative records</t>
+          <t>Nationals</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>المصدر</t>
+          <t>المواطنة</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>السجلات الادارية</t>
+          <t>أردني</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Administrative data</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بيانات إدارية </t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Statistical Yearbook 2012</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>الكتاب الاحصائي 2012</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Statistical Yearbook 2015</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>الكتاب الاحصائي 2015</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Libyan Family Health Survey 2014</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>المسح الليبي لصحة الأسرة 2014</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey 2014</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة  2014</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey 2014</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة 2014</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey, Preliminary Report 2014</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة التقرير الأولي 2014</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey, Preliminary Report 2014</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة التقرير الاولي 2014</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey, Main Report 2014</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة التقرير الرئيسي 2014</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Libyan National Family Health Survey, Main Report 2014</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>المسح الوطني الليبي لصحة الأسرة الرئيسي 2014</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Health Documentation and Information Center 2019</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>مركز التوثيق و المعلومات الصحة 2019</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Information and Documentation Center, Ministry of Health 2023</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>مركز المعلومات والثوتيق بوزارة الصحة 2023</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2024 - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكتى لسنة 2024- المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2024 - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكنة لسنة 2024 - المعهد الوطني للإخصاء</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2014</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكنى 2014</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2014 - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكنى لسنة 2014- المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2024 - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكنى لسنة 2024 - المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2024 - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والسكنى لسنة 2024- المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey, Second Quarter - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t xml:space="preserve">المسح الوطني حول السكان والتشغيل - الثلاثي الثاني - المعهد الوطني للاحصاء </t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>المسح الوطني حول السكان والتشغيل- المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>المسح الوطني حول السكان والتشغيل -  المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>المسح الوطني حول السكان والتشغيل - المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>المسح الوطني حول السكان والتشغيل - المعهد الوطني للحصاء</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>National Child Labour Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>المسح الوطني حول تشغيل الأطفال - المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>National Population and Employment Survey - National Institute of Statistics</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>المسح الوطني للسكان والتشغيل - المعهد الوطني للإحصاء</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>International Labour Organization (ILO)</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>منظمة العمل الدولية</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Nationality</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Nationals</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>المواطنة</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>أردني</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Population data, estimated for year-end, 2010-2022</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>البيانات السكانية مقدرة لنهاية العام للسنوات 2010-2022</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2015 (2015/11/31)</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والمساكن 2015 (2015/11/31)</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2015 (2015/11/31)</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">التعداد العام للسكان والمساكن 2015 (2015/11/31) </t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2015 (2015/11/31) http://www.dos.gov.jo/dos_home_a/main/population/census2015/HousingUnits/Housing_2.16.pdf</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والمساكن 2015 (2015/11/31) http://www.dos.gov.jo/dos_home_a/main/population/census2015/HousingUnits/Housing_2.16.pdf</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>General Population and Housing Census 2015 (2015/11/31) - data include non-Jordanians residing in the Kingdom</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>التعداد العام للسكان والمساكن 2015 (2015/11/31) البيانات تشمل غير الاردنيين المقيمين داخل المملكة</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Sharia Courts</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>المحاكم الشرعية</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Sharia Courts https://jorinfo.dos.gov.jo/Databank/pxweb/ar/Divorce_Marriage/Divorce_Marriage__Marrige/Table_5.px/table/tableViewLayout2/</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>المحاكم الشرعية https://jorinfo.dos.gov.jo/Databank/pxweb/ar/Divorce_Marriage/Divorce_Marriage__Marrige/Table_5.px/table/tableViewLayout2/</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>National Center for Security and Crisis Management (NCSCM)</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>المركز الوطني للأمن وإدارة الأزمات</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Jordan Statistical Yearbook</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>دائرة الإحصاءات العامة، الكتاب الإحصائي السنوي الأردن</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Department of Statistics</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Department of Statistics / Employment and Unemployment Survey</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة / مسح العمالة والبطالة</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Jordan Population and Family Health Survey</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة ، مسح السكان والصحة الأسرية</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Statistical Yearbook</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة، الكتاب الاحصائي السنوي</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Jordan Population and Family Health Survey</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة، مسح السكان والصحة الأسرية</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Jordan Population and Family Health Survey</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة، مسح السكان والصحة الأسريةدائرة الاحصاءات العامة، مسح السكان والصحة الأسرية</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Labour Force Survey</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة، مسح قوة العمل</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Department of Statistics, Labour Force Survey</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>دائرة الاحصاءات العامة،مسح قوة العمل</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Civil Status and Passports Department</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>دائرة الاحوال المدنية والجوازات</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Ministry of Health / Causes of Death Bulletin</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>وزارة الصحة/نشرة أسباب الوفيات</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Household Income and Expenditure Survey</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>مسح إنفاق ودخل الأسرة</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Household Income and Expenditure Survey</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>مسح دخل وإنفاق الاسرة</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/prevalence-of-obesity-among-adults-bmi--30-(crude-estimate)-(-)</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/prevalence-of-obesity-among-adults-bmi--30-(crude-estimate)-(-)</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/current-health-expenditure-(che)-per-capita-in-us-dollar</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/current-health-expenditure-(che)-per-capita-in-us-dollar</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-per-capita-in-us</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-per-capita-in-us</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-as-percentage-of-gross-domestic-product-(gdp)-(-)</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-as-percentage-of-gross-domestic-product-(gdp)-(-)</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-as-percentage-of-general-government-expenditure-(gge)</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>المصدر</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/domestic-general-government-health-expenditure-(gghe-d)-as-percentage-of-general-government-expenditure-(gge)</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
